--- a/02_加值成品/八下/八下2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下2-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下2-2 還原反應　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二下學期 八下2-2 還原反應　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>物質失去氧的反應是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>同時成對</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>氧化物</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>還原反應</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>失氧</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>還原常與什麼反應同時發生？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>氧化</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>還原</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>銅與二氧化碳</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>同時成對</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>得到氧的物質被？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>氧化</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>同時等量</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>還原反應</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>得氧</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>失去氧的物質被？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>同時等量</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>還原</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>還原反應</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>失氧</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>活性大的金屬容易？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>還原劑</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>失電子被氧化</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氧化</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>活潑</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>鎂加熱氧化銅,銅被？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>還原</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>還原劑</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>失電子被氧化</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>銅離子</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>失氧</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>氧化還原反應中氧如何？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>A活性大於B則可</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>由還原劑轉到氧化劑</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>由一方轉到另一方</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>鎂被氧化、氧化銅被還原</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>轉移</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>提煉金屬常需要哪種反應？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>還原</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>還原反應</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>取出金屬</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>還原是物質失去什麼？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>同時等量</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>銅與二氧化碳</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>氧</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>銅離子</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>失氧</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>氧化與還原通常如何發生？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>還原劑</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>同時成對</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>失電子被氧化</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>還原</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>成對</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下2-2 還原反應　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二下學期 八下2-2 還原反應　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>CuO+H₂→Cu+H₂O中CuO被？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>還原</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>銅與二氧化碳</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>還原反應</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>同時等量</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>失氧</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>上題中H₂被？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>銅與二氧化碳</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>氧化</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>銅離子</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>得氧</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>鎂比銅活性大,鎂能還原氧化銅嗎？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>氧化</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>能</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>同時成對</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>活性大</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>氧化還原中電子如何(定性)？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>鎂被氧化、氧化銅被還原</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>由一方轉到另一方</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>由還原劑轉到氧化劑</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>銅離子被還原成銅</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>轉移</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>碳還原氧化銅生成？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>銅與二氧化碳</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>還原</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>氧化物</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>銅離子</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>產物</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>活性小金屬能還原活性大金屬氧化物嗎？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>同時等量</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>還原</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>不能</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>還原反應</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>活性不足</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>氧化與還原數量關係？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>失電子被氧化</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>還原反應</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>同時等量</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>還原</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>鐵釘泡硫酸銅表面析出銅因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>移高中,國中重概念</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>鐵較活潑置換銅</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>由一方轉到另一方</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>有得氧必有失氧,電子守恆</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>活性</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>氧化銅被碳還原生成？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>銅與二氧化碳</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>同時等量</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
           <t>還原</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="34" customHeight="1">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>還原</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>活性大金屬可還原活性小金屬的？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>氧化</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>還原</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>氧化物</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>同時等量</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>置換</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二下學期 八下2-2 還原反應　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二下學期 八下2-2 還原反應　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>鎂還原氧化銅中誰被氧化誰被還原？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>鐵較活潑置換銅</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>由一方轉到另一方</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>鎂被氧化、氧化銅被還原</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>由還原劑轉到氧化劑</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>成對</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何氧化還原必成對發生？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>自己先被氧化保護食物</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>由一方轉到另一方</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>有得氧必有失氧,電子守恆</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>鎂被氧化、氧化銅被還原</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>守恆</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>用金屬活性順序判斷A能否還原B氧化物？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>A活性大於B則可</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>由一方轉到另一方</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>自己先被氧化保護食物</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>鐵較活潑置換銅</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>活性比較</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>氫還原氧化銅,氫的角色？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>自己先被氧化保護食物</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>鐵較活潑置換銅</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>鎂被氧化、氧化銅被還原</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>還原劑(自己被氧化)</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>角色</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>鐵置換硫酸銅溶液,何者被還原？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>銅離子被還原成銅</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>有得氧必有失氧,電子守恆</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>鐵較活潑置換銅</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>由一方轉到另一方</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>置換</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>為何課綱移除冶金製程細節？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>自己先被氧化保護食物</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>鎂被氧化、氧化銅被還原</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>移高中,國中重概念</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>A活性大於B則可</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>抗氧化劑保護食物原理？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>自己先被氧化保護食物</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>鐵較活潑置換銅</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>有得氧必有失氧,電子守恆</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>由還原劑轉到氧化劑</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>犧牲</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>活性:鎂&gt;鋅&gt;鐵&gt;銅,誰最易被還原(當離子)？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>銅離子</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>不能</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>能</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>還原反應</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>活性小易還原</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>氫氣還原氧化銅實驗中氫扮演？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>還原劑</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>還原</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>失電子被氧化</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>還原劑</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>用鎂&gt;鐵&gt;銅判斷鎂能否還原氧化鐵？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>銅離子被還原成銅</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>有得氧必有失氧,電子守恆</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>能,鎂活性較大</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>A活性大於B則可</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>活性</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八下/八下2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下2-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>失氧</t>
+          <t>失氧：一種物質原本帶有氧，反應後把氧釋放出去，這個過程就叫還原反應</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：一方失去氧被還原時，另一方一定會得到那個氧被氧化，兩者總是一起發生</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>得氧</t>
+          <t>得氧：物質如果在反應中得到了氧原子，就代表它被氧化了</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>失氧</t>
+          <t>失氧：物質如果在反應中失去了氧原子，就代表它被還原了</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>活潑</t>
+          <t>活潑：活性越大的金屬，越容易把自己的電子讓出去，也就是越容易被氧化</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>失氧</t>
+          <t>失氧：氧化銅裡的氧被活性更大的鎂搶走了，氧化銅失去氧變回銅，所以銅被還原</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>轉移</t>
+          <t>轉移：氧原子並沒有消失，而是從失去它的一方，轉移到得到它的另一方身上</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>取出金屬</t>
+          <t>取出金屬：金屬礦石大多是金屬的氧化物，要把氧拿掉才能得到純金屬，所以需要還原反應</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>失氧</t>
+          <t>失氧：還原反應的基本定義是物質失去原本結合的氧，是氧化的相反過程</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：氧化反應和還原反應通常同時發生在同一個反應中，一種物質被氧化，同時另一種物質就被還原，兩者成對出現</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>失氧</t>
+          <t>失氧：氧化銅CuO反應後失去氧原子變成銅Cu，所以氧化銅是被還原的一方</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>得氧</t>
+          <t>得氧：氫氣H2在反應中得到氧原子變成水H2O，所以氫氣是被氧化的一方</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>活性大</t>
+          <t>活性大：活性大的鎂能搶走氧化銅裡的氧，把銅還原出來，自己則變成氧化鎂</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>轉移</t>
+          <t>轉移：讓出電子的一方叫還原劑，接收電子的一方叫氧化劑，電子就是從還原劑跑向氧化劑</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>產物</t>
+          <t>產物：碳把氧化銅裡的氧搶走變成二氧化碳，氧化銅則失去氧變回純銅</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>活性不足</t>
+          <t>活性不足：活性小的金屬搶不贏活性大金屬對氧的吸引力，所以沒辦法把它的氧化物還原</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：有多少氧原子被一方拿走，就有多少氧原子被另一方失去，兩者數量一定相等</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>活性</t>
+          <t>活性：鐵的活性比銅大，會把溶液中銅離子的位置搶過來，讓銅析出附著在鐵釘表面</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>還原</t>
+          <t>還原：碳從氧化銅中把氧搶走(還原氧化銅)，生成純銅，而碳自己結合了氧變成二氧化碳(碳被氧化)</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>置換</t>
+          <t>置換：活性較大的金屬有較強的能力搶走氧，可以把活性較小金屬的氧化物中的氧奪走，使活性小的金屬還原析出</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>成對</t>
+          <t>成對：鎂搶走氧化銅裡的氧變成氧化鎂（鎂被氧化），氧化銅則失去氧變回銅（被還原）</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>守恆</t>
+          <t>守恆：氧原子和電子都不會憑空產生或消失，一方得到就必定有另一方同時失去</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>活性比較</t>
+          <t>活性比較：只要A金屬在活性順序表上排在B金屬前面，A就有能力把B的氧化物還原</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>角色</t>
+          <t>角色：氫氣把氧化銅還原成銅，但它自己卻在過程中得到氧變成水，所以氫氣本身是被氧化的還原劑</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>置換</t>
+          <t>置換：溶液中的銅離子接受了鐵讓出的電子，變回中性的銅原子析出，這就是被還原</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：實際工業煉金屬的複雜製程留給高中學習，國中階段只要先掌握氧化還原的基本概念</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>犧牲</t>
+          <t>犧牲：抗氧化劑比食物更容易被氧氣搶先反應掉，等於代替食物先氧化，保護食物不變質</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>活性小易還原</t>
+          <t>活性小易還原：活性越小的金屬離子，代表它越不想保持離子狀態，越容易接受電子被還原成金屬</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>還原劑</t>
+          <t>還原劑：氫氣把氧化銅中的氧奪走，使氧化銅還原成銅，氫氣自己則變成水，在這個反應中氫氣扮演使別人被還原的還原劑角色</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>活性</t>
+          <t>活性：金屬活性順序中鎂排在鐵前面，代表鎂比鐵更活潑、更容易搶氧，因此鎂能夠把氧化鐵中的氧奪走，使鐵被還原析出</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八下/八下2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八下/八下2-2_三種難度測驗卷.xlsx
@@ -563,17 +563,17 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>同時成對</t>
+          <t>能</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>氧</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
           <t>氧化物</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>不能</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -608,12 +608,12 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>還原</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>銅與二氧化碳</t>
+          <t>還原反應</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -648,17 +648,17 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>同時等量</t>
+          <t>還原反應</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>氧</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>還原反應</t>
+          <t>同時成對</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -683,12 +683,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>能</t>
+          <t>氧化物</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>同時等量</t>
+          <t>氧</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>還原反應</t>
+          <t>氧化</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>氧化</t>
+          <t>還原</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>還原劑</t>
+          <t>失電子被氧化</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>失電子被氧化</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>銅離子</t>
+          <t>氧化</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>還原</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>能</t>
+          <t>氧</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>氧</t>
+          <t>失電子被氧化</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>同時等量</t>
+          <t>還原</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>銅與二氧化碳</t>
+          <t>銅離子</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>銅離子</t>
+          <t>同時成對</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>還原反應</t>
+          <t>氧化</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>同時等量</t>
+          <t>氧化物</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
@@ -1079,12 +1079,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>氧</t>
+          <t>還原劑</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>銅與二氧化碳</t>
+          <t>不能</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>銅離子</t>
+          <t>還原反應</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>氧化</t>
+          <t>氧</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>不能</t>
+          <t>還原反應</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>同時成對</t>
+          <t>氧化物</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -1204,17 +1204,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>還原</t>
+          <t>銅離子</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>氧化物</t>
+          <t>同時等量</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>銅離子</t>
+          <t>還原反應</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>同時等量</t>
+          <t>同時成對</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>還原</t>
+          <t>還原劑</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>還原反應</t>
+          <t>失電子被氧化</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>同時等量</t>
+          <t>失電子被氧化</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>還原</t>
+          <t>能</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>氧</t>
+          <t>銅離子</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
@@ -1399,12 +1399,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>氧化</t>
+          <t>還原</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>還原</t>
+          <t>還原反應</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -1840,17 +1840,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>還原</t>
+          <t>銅離子</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
+          <t>氧化物</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
           <t>失電子被氧化</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>氧</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
